--- a/data/trans_bre/P57_R2-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P57_R2-Provincia-trans_bre.xlsx
@@ -601,22 +601,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-13,09; 1,73</t>
+          <t>-13,84; 1,9</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-18,27; -1,9</t>
+          <t>-17,5; -0,84</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-37,53; 6,22</t>
+          <t>-39,19; 6,75</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-55,98; -8,94</t>
+          <t>-53,58; -4,05</t>
         </is>
       </c>
     </row>
@@ -661,22 +661,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-8,96; 2,64</t>
+          <t>-8,55; 2,73</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-11,38; 1,46</t>
+          <t>-12,04; 1,44</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-24,02; 8,22</t>
+          <t>-22,83; 8,63</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-14,77; 2,06</t>
+          <t>-15,57; 2,08</t>
         </is>
       </c>
     </row>
@@ -721,22 +721,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,64; 5,46</t>
+          <t>-8,69; 4,8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-16,28; -1,66</t>
+          <t>-16,29; -1,76</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-25,24; 20,62</t>
+          <t>-25,91; 17,08</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-31,49; -4,2</t>
+          <t>-30,76; -3,35</t>
         </is>
       </c>
     </row>
@@ -781,22 +781,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-12,57; 1,92</t>
+          <t>-13,37; 0,96</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-23,8; 3,02</t>
+          <t>-25,79; 2,78</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-28,76; 5,21</t>
+          <t>-29,88; 2,98</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-53,24; 7,39</t>
+          <t>-54,0; 7,1</t>
         </is>
       </c>
     </row>
@@ -841,22 +841,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-9,9; 2,48</t>
+          <t>-10,85; 2,4</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-11,68; 4,57</t>
+          <t>-12,07; 3,91</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-53,43; 22,07</t>
+          <t>-57,09; 22,17</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-26,15; 14,05</t>
+          <t>-26,53; 11,52</t>
         </is>
       </c>
     </row>
@@ -901,22 +901,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-14,58; 2,44</t>
+          <t>-15,42; 1,52</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-5,64; 9,79</t>
+          <t>-5,97; 8,87</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-26,54; 5,27</t>
+          <t>-28,12; 3,08</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-10,48; 21,43</t>
+          <t>-10,54; 19,33</t>
         </is>
       </c>
     </row>
@@ -961,22 +961,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-8,66; 1,05</t>
+          <t>-8,17; 2,34</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-32,83; -2,58</t>
+          <t>-32,06; -3,21</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-26,88; 4,05</t>
+          <t>-25,41; 8,82</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-70,59; -6,15</t>
+          <t>-66,43; -6,91</t>
         </is>
       </c>
     </row>
@@ -1021,22 +1021,22 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-8,09; 0,23</t>
+          <t>-7,83; 0,03</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-48,21; -7,11</t>
+          <t>-46,97; -7,11</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-36,37; 0,48</t>
+          <t>-35,87; 0,14</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-60,51; -17,35</t>
+          <t>-61,39; -17,1</t>
         </is>
       </c>
     </row>
@@ -1081,22 +1081,22 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-6,2; -1,85</t>
+          <t>-6,38; -1,99</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-27,7; -7,58</t>
+          <t>-23,38; -6,57</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-19,64; -6,15</t>
+          <t>-20,02; -6,6</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-45,02; -16,0</t>
+          <t>-41,26; -13,9</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P57_R2-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P57_R2-Provincia-trans_bre.xlsx
@@ -578,7 +578,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>-8,83</t>
+          <t>-4,84</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-34,69%</t>
+          <t>-20,79%</t>
         </is>
       </c>
     </row>
@@ -601,22 +601,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-13,84; 1,9</t>
+          <t>-14,17; 1,64</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-17,5; -0,84</t>
+          <t>-11,01; 1,39</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-39,19; 6,75</t>
+          <t>-40,44; 6,41</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-53,58; -4,05</t>
+          <t>-40,56; 7,9</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>-5,06</t>
+          <t>-4,75</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-6,93%</t>
+          <t>-6,51%</t>
         </is>
       </c>
     </row>
@@ -661,22 +661,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-8,55; 2,73</t>
+          <t>-8,63; 2,96</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-12,04; 1,44</t>
+          <t>-10,46; 1,86</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-22,83; 8,63</t>
+          <t>-22,97; 9,39</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-15,57; 2,08</t>
+          <t>-13,78; 2,76</t>
         </is>
       </c>
     </row>
@@ -698,7 +698,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>-9,43</t>
+          <t>-8,45</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-19,58%</t>
+          <t>-17,83%</t>
         </is>
       </c>
     </row>
@@ -721,22 +721,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,69; 4,8</t>
+          <t>-8,06; 5,83</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-16,29; -1,76</t>
+          <t>-15,02; -1,69</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-25,91; 17,08</t>
+          <t>-23,39; 22,67</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-30,76; -3,35</t>
+          <t>-29,17; -3,72</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>-8,04</t>
+          <t>-1,45</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-19,84%</t>
+          <t>-3,42%</t>
         </is>
       </c>
     </row>
@@ -781,22 +781,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-13,37; 0,96</t>
+          <t>-12,07; 1,64</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-25,79; 2,78</t>
+          <t>-9,76; 7,78</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-29,88; 2,98</t>
+          <t>-27,62; 4,33</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-54,0; 7,1</t>
+          <t>-20,11; 21,16</t>
         </is>
       </c>
     </row>
@@ -818,7 +818,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>-4,28</t>
+          <t>-5,08</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-10,63%</t>
+          <t>-12,47%</t>
         </is>
       </c>
     </row>
@@ -841,22 +841,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-10,85; 2,4</t>
+          <t>-10,98; 2,27</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-12,07; 3,91</t>
+          <t>-12,94; 2,37</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-57,09; 22,17</t>
+          <t>-56,21; 19,75</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-26,53; 11,52</t>
+          <t>-28,62; 6,24</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1,81</t>
+          <t>2,36</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>4,8%</t>
         </is>
       </c>
     </row>
@@ -901,22 +901,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-15,42; 1,52</t>
+          <t>-14,84; 2,42</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-5,97; 8,87</t>
+          <t>-5,07; 10,06</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-28,12; 3,08</t>
+          <t>-26,62; 4,96</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-10,54; 19,33</t>
+          <t>-9,71; 22,51</t>
         </is>
       </c>
     </row>
@@ -938,7 +938,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>-14,57</t>
+          <t>-4,71</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -948,7 +948,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-32,68%</t>
+          <t>-10,67%</t>
         </is>
       </c>
     </row>
@@ -961,22 +961,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-8,17; 2,34</t>
+          <t>-8,49; 1,62</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-32,06; -3,21</t>
+          <t>-10,03; 1,19</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-25,41; 8,82</t>
+          <t>-26,21; 6,16</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-66,43; -6,91</t>
+          <t>-21,06; 2,99</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>-23,74</t>
+          <t>-8,66</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-41,62%</t>
+          <t>-20,67%</t>
         </is>
       </c>
     </row>
@@ -1021,22 +1021,22 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-7,83; 0,03</t>
+          <t>-7,52; 0,61</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-46,97; -7,11</t>
+          <t>-13,38; -3,45</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-35,87; 0,14</t>
+          <t>-34,03; 5,81</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-61,39; -17,1</t>
+          <t>-29,77; -8,92</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>-12,7</t>
+          <t>-5,17</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-25,08%</t>
+          <t>-11,14%</t>
         </is>
       </c>
     </row>
@@ -1081,22 +1081,22 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-6,38; -1,99</t>
+          <t>-6,08; -1,59</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-23,38; -6,57</t>
+          <t>-7,6; -2,74</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-20,02; -6,6</t>
+          <t>-19,39; -5,48</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-41,26; -13,9</t>
+          <t>-16,07; -6,13</t>
         </is>
       </c>
     </row>
